--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_THE FITZGERALD EL PILAR.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>91.8212</v>
+        <v>77.58629999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>68.45310000000001</v>
+        <v>57.2324</v>
       </c>
       <c r="F2" t="n">
-        <v>23.368</v>
+        <v>20.3539</v>
       </c>
       <c r="G2" t="n">
         <v>18.4437</v>
@@ -610,13 +610,13 @@
         <v>64.1399</v>
       </c>
       <c r="S2" t="n">
-        <v>28.938</v>
+        <v>14.7031</v>
       </c>
       <c r="T2" t="n">
-        <v>17.8596</v>
+        <v>6.639</v>
       </c>
       <c r="U2" t="n">
-        <v>11.0783</v>
+        <v>8.064</v>
       </c>
       <c r="V2" t="n">
         <v>44.44</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>86.4777</v>
+        <v>72.87140000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>77.3609</v>
+        <v>66.2496</v>
       </c>
       <c r="F3" t="n">
-        <v>9.116399999999999</v>
+        <v>6.6213</v>
       </c>
       <c r="G3" t="n">
         <v>21.3679</v>
@@ -688,13 +688,13 @@
         <v>52.5949</v>
       </c>
       <c r="S3" t="n">
-        <v>24.3693</v>
+        <v>10.7628</v>
       </c>
       <c r="T3" t="n">
-        <v>14.7043</v>
+        <v>3.593</v>
       </c>
       <c r="U3" t="n">
-        <v>9.6648</v>
+        <v>7.1698</v>
       </c>
       <c r="V3" t="n">
         <v>22.4151</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>43.4795</v>
+        <v>54.4309</v>
       </c>
       <c r="E4" t="n">
-        <v>34.6903</v>
+        <v>49.115</v>
       </c>
       <c r="F4" t="n">
-        <v>8.789</v>
+        <v>5.3157</v>
       </c>
       <c r="G4" t="n">
         <v>22.7293</v>
@@ -766,13 +766,13 @@
         <v>57.5427</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.1945</v>
+        <v>5.7569</v>
       </c>
       <c r="T4" t="n">
-        <v>-16.5845</v>
+        <v>-2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>11.3899</v>
+        <v>7.9169</v>
       </c>
       <c r="V4" t="n">
         <v>28.1437</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>26.7469</v>
+        <v>18.7545</v>
       </c>
       <c r="E6" t="n">
-        <v>34.3503</v>
+        <v>18.7545</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.603199999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6305</v>
+        <v>18.7545</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8861</v>
+        <v>8.127599999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>9.5167</v>
+        <v>10.6267</v>
       </c>
       <c r="J6" t="n">
-        <v>27.8062</v>
+        <v>18.7545</v>
       </c>
       <c r="K6" t="n">
-        <v>11.6486</v>
+        <v>8.127599999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>16.1574</v>
+        <v>10.6267</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.1756</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.5349</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.6409</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>12.0952</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.991</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>34.0856</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>15.2153</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>13.9025</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3126</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-8.1937</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>14.6325</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-22.8262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>18.7545</v>
+        <v>16.8128</v>
       </c>
       <c r="E7" t="n">
-        <v>18.7545</v>
+        <v>23.9664</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-7.1535</v>
       </c>
       <c r="G7" t="n">
-        <v>18.7545</v>
+        <v>7.6305</v>
       </c>
       <c r="H7" t="n">
-        <v>8.127599999999999</v>
+        <v>-1.8861</v>
       </c>
       <c r="I7" t="n">
-        <v>10.6267</v>
+        <v>9.5167</v>
       </c>
       <c r="J7" t="n">
-        <v>18.7545</v>
+        <v>27.8062</v>
       </c>
       <c r="K7" t="n">
-        <v>8.127599999999999</v>
+        <v>11.6486</v>
       </c>
       <c r="L7" t="n">
-        <v>10.6267</v>
+        <v>16.1574</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-20.1756</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-13.5349</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-6.6409</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>12.0952</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-21.991</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>34.0856</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.2809</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5186</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.7625</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-8.1937</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>14.6325</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-22.8262</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SILVA</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9.0435</v>
+        <v>13.8166</v>
       </c>
       <c r="E9" t="n">
-        <v>10.487</v>
+        <v>8.089799999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4436</v>
+        <v>5.7268</v>
       </c>
       <c r="G9" t="n">
-        <v>4.974900000000001</v>
+        <v>-0.5918000000000003</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5251</v>
+        <v>4.788900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4498</v>
+        <v>-5.3806</v>
       </c>
       <c r="J9" t="n">
-        <v>8.1297</v>
+        <v>9.0305</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2045</v>
+        <v>11.1394</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9251</v>
+        <v>-2.1086</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1547</v>
+        <v>-9.622400000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6793</v>
+        <v>-6.3505</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4755</v>
+        <v>-3.2716</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4819</v>
+        <v>3.6651</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-12.095</v>
       </c>
       <c r="R9" t="n">
-        <v>5.3144</v>
+        <v>15.7602</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9917</v>
+        <v>3.1164</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3786000000000001</v>
+        <v>2.5033</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3706</v>
+        <v>0.6133000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5785</v>
+        <v>7.6268</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8113</v>
+        <v>8.651</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2328</v>
+        <v>-1.0242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>8.815</v>
+        <v>8.704800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9193</v>
+        <v>2.9082</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8958</v>
+        <v>5.7967</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5918000000000003</v>
+        <v>-2.5034</v>
       </c>
       <c r="H10" t="n">
-        <v>4.788900000000001</v>
+        <v>-1.7055</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.3806</v>
+        <v>-0.7977999999999995</v>
       </c>
       <c r="J10" t="n">
-        <v>9.0305</v>
+        <v>0.8346000000000009</v>
       </c>
       <c r="K10" t="n">
-        <v>11.1394</v>
+        <v>0.4444999999999998</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1086</v>
+        <v>0.3902</v>
       </c>
       <c r="M10" t="n">
-        <v>-9.622400000000001</v>
+        <v>-3.3385</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.3505</v>
+        <v>-2.1504</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2716</v>
+        <v>-1.1881</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6651</v>
+        <v>12.095</v>
       </c>
       <c r="Q10" t="n">
-        <v>-12.095</v>
+        <v>-5.3145</v>
       </c>
       <c r="R10" t="n">
-        <v>15.7602</v>
+        <v>17.4094</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8852</v>
+        <v>4.7212</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3327</v>
+        <v>2.6209</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.2179</v>
+        <v>2.1003</v>
       </c>
       <c r="V10" t="n">
-        <v>7.6268</v>
+        <v>-5.6079</v>
       </c>
       <c r="W10" t="n">
-        <v>8.651</v>
+        <v>4.7667</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0242</v>
+        <v>-10.3747</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>E. SILVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>8.080599999999999</v>
+        <v>8.4091</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8967</v>
+        <v>9.8279</v>
       </c>
       <c r="F11" t="n">
-        <v>4.183999999999999</v>
+        <v>-1.4188</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5034</v>
+        <v>4.974900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7055</v>
+        <v>1.5251</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7977999999999995</v>
+        <v>3.4498</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8346000000000009</v>
+        <v>8.1297</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4444999999999998</v>
+        <v>3.2045</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3902</v>
+        <v>4.9251</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3385</v>
+        <v>-3.1547</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1504</v>
+        <v>-1.6793</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1881</v>
+        <v>-1.4755</v>
       </c>
       <c r="P11" t="n">
-        <v>12.095</v>
+        <v>3.4819</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.3145</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>17.4094</v>
+        <v>5.3144</v>
       </c>
       <c r="S11" t="n">
-        <v>4.097</v>
+        <v>-1.6262</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6094</v>
+        <v>-0.2804</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4876</v>
+        <v>-1.3457</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.6079</v>
+        <v>1.5785</v>
       </c>
       <c r="W11" t="n">
-        <v>4.7667</v>
+        <v>3.8113</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.3747</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7.101900000000001</v>
+        <v>7.0144</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5586</v>
+        <v>5.1739</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5433</v>
+        <v>1.8405</v>
       </c>
       <c r="G12" t="n">
         <v>1.8913</v>
@@ -1390,13 +1390,13 @@
         <v>3.4819</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3257</v>
+        <v>0.2382</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1622</v>
+        <v>-0.2223</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1634</v>
+        <v>0.4609</v>
       </c>
       <c r="V12" t="n">
         <v>5.0679</v>
@@ -1423,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>3.194900000000001</v>
+        <v>3.660699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8534</v>
+        <v>2.6751</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3414999999999999</v>
+        <v>0.9855999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>1.8984</v>
@@ -1468,13 +1468,13 @@
         <v>4.3982</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6173</v>
+        <v>-0.1515</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2964</v>
+        <v>-0.4747</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3209</v>
+        <v>0.3231</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5682</v>
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0286</v>
+        <v>1.6916</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03100000000000014</v>
+        <v>-0.6901000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0597</v>
+        <v>2.3817</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4770999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>3.4818</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8173</v>
+        <v>0.4802</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6087</v>
+        <v>0.9494</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7913000000000001</v>
+        <v>-0.4693</v>
       </c>
       <c r="V14" t="n">
         <v>0.9554999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9126999999999997</v>
+        <v>1.1181</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3263</v>
+        <v>-1.4225</v>
       </c>
       <c r="F15" t="n">
-        <v>2.239</v>
+        <v>2.5406</v>
       </c>
       <c r="G15" t="n">
         <v>1.8309</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2691</v>
+        <v>-0.0635</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3651</v>
+        <v>0.2689</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6340999999999999</v>
+        <v>-0.3323</v>
       </c>
       <c r="V15" t="n">
         <v>0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4342</v>
+        <v>-0.5085</v>
       </c>
       <c r="E16" t="n">
         <v>-0.9163</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4821</v>
+        <v>0.4078</v>
       </c>
       <c r="G16" t="n">
         <v>0.2564</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2257</v>
+        <v>0.1514</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2257</v>
+        <v>0.1514</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7096</v>
+        <v>-1.322</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7646000000000001</v>
+        <v>-0.4762000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9448</v>
+        <v>-0.8458</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2333</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9973</v>
+        <v>-0.6097</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7527</v>
+        <v>-0.4642</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2446</v>
+        <v>-0.1456</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5785</v>
@@ -1813,13 +1813,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4474</v>
+        <v>-3.416</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.5891</v>
+        <v>-7.8636</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1417</v>
+        <v>4.4476</v>
       </c>
       <c r="G18" t="n">
         <v>0.5497000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>8.0633</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1269</v>
+        <v>-2.0955</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6318</v>
+        <v>-0.9063</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.495</v>
+        <v>-1.189</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7706000000000001</v>
@@ -1891,13 +1891,13 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.6958</v>
+        <v>-3.8277</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.0678</v>
+        <v>-7.609</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3721</v>
+        <v>3.7812</v>
       </c>
       <c r="G19" t="n">
         <v>-5.4032</v>
@@ -1936,13 +1936,13 @@
         <v>10.9953</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.5807</v>
+        <v>-2.7128</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.444900000000001</v>
+        <v>-1.9859</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1359</v>
+        <v>-0.7269</v>
       </c>
       <c r="V19" t="n">
         <v>0.6231</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. REOS CAMPOS</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.112299999999999</v>
+        <v>-4.208099999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1116</v>
+        <v>-19.3645</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0009</v>
+        <v>15.1564</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5385</v>
+        <v>-22.1289</v>
       </c>
       <c r="H20" t="n">
-        <v>3.298</v>
+        <v>-5.9854</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.8363</v>
+        <v>-16.1434</v>
       </c>
       <c r="J20" t="n">
-        <v>7.1679</v>
+        <v>-5.708399999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>8.579700000000001</v>
+        <v>9.3391</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4117</v>
+        <v>-15.0477</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.7065</v>
+        <v>-16.4202</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.2817</v>
+        <v>-15.3244</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.4248</v>
+        <v>-1.0956</v>
       </c>
       <c r="P20" t="n">
-        <v>-6.7805</v>
+        <v>14.1106</v>
       </c>
       <c r="Q20" t="n">
-        <v>-14.8439</v>
+        <v>-26.3894</v>
       </c>
       <c r="R20" t="n">
-        <v>8.0634</v>
+        <v>40.4997</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.317</v>
+        <v>-4.249099999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2367</v>
+        <v>-1.5881</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0802</v>
+        <v>-2.6608</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5237</v>
+        <v>8.0589</v>
       </c>
       <c r="W20" t="n">
-        <v>3.8009</v>
+        <v>14.3212</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2773</v>
+        <v>-6.2622</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>M. REOS CAMPOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.7014</v>
+        <v>-6.6141</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.099500000000001</v>
+        <v>-3.9437</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.6015</v>
+        <v>-2.6705</v>
       </c>
       <c r="G21" t="n">
-        <v>8.9078</v>
+        <v>-2.5385</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8651</v>
+        <v>3.298</v>
       </c>
       <c r="I21" t="n">
-        <v>10.7732</v>
+        <v>-5.8363</v>
       </c>
       <c r="J21" t="n">
-        <v>23.4708</v>
+        <v>7.1679</v>
       </c>
       <c r="K21" t="n">
-        <v>12.0844</v>
+        <v>8.579700000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>11.3861</v>
+        <v>-1.4117</v>
       </c>
       <c r="M21" t="n">
-        <v>-14.563</v>
+        <v>-9.7065</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.95</v>
+        <v>-5.2817</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6128999999999998</v>
+        <v>-4.4248</v>
       </c>
       <c r="P21" t="n">
-        <v>-11.1787</v>
+        <v>-6.7805</v>
       </c>
       <c r="Q21" t="n">
-        <v>-39.0339</v>
+        <v>-14.8439</v>
       </c>
       <c r="R21" t="n">
-        <v>27.8548</v>
+        <v>8.0634</v>
       </c>
       <c r="S21" t="n">
-        <v>8.3994</v>
+        <v>0.1811000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>7.1105</v>
+        <v>-0.06890000000000006</v>
       </c>
       <c r="U21" t="n">
-        <v>1.289</v>
+        <v>0.2499</v>
       </c>
       <c r="V21" t="n">
-        <v>-16.8299</v>
+        <v>2.5237</v>
       </c>
       <c r="W21" t="n">
-        <v>7.3527</v>
+        <v>3.8009</v>
       </c>
       <c r="X21" t="n">
-        <v>-24.1826</v>
+        <v>-1.2773</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.1683</v>
+        <v>-13.509</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.5374</v>
+        <v>-5.4941</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.6309</v>
+        <v>-8.015000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-19.9719</v>
+        <v>8.9078</v>
       </c>
       <c r="H22" t="n">
-        <v>-14.2684</v>
+        <v>-1.8651</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.7035</v>
+        <v>10.7732</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.194800000000001</v>
+        <v>23.4708</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.925</v>
+        <v>12.0844</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.27</v>
+        <v>11.3861</v>
       </c>
       <c r="M22" t="n">
-        <v>-15.7769</v>
+        <v>-14.563</v>
       </c>
       <c r="N22" t="n">
-        <v>-12.3435</v>
+        <v>-13.95</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.4331</v>
+        <v>-0.6128999999999998</v>
       </c>
       <c r="P22" t="n">
-        <v>15.0269</v>
+        <v>-11.1787</v>
       </c>
       <c r="Q22" t="n">
-        <v>-12.4618</v>
+        <v>-39.0339</v>
       </c>
       <c r="R22" t="n">
-        <v>27.4886</v>
+        <v>27.8548</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.9608</v>
+        <v>5.5917</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0691</v>
+        <v>2.7159</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.8918</v>
+        <v>2.8759</v>
       </c>
       <c r="V22" t="n">
-        <v>-10.2626</v>
+        <v>-16.8299</v>
       </c>
       <c r="W22" t="n">
-        <v>3.1882</v>
+        <v>7.3527</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.4509</v>
+        <v>-24.1826</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>-24.2327</v>
+        <v>-14.2039</v>
       </c>
       <c r="E23" t="n">
-        <v>-32.8406</v>
+        <v>-12.2701</v>
       </c>
       <c r="F23" t="n">
-        <v>8.608000000000001</v>
+        <v>-1.9343</v>
       </c>
       <c r="G23" t="n">
-        <v>-22.1289</v>
+        <v>-19.9719</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.9854</v>
+        <v>-14.2684</v>
       </c>
       <c r="I23" t="n">
-        <v>-16.1434</v>
+        <v>-5.7035</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.708399999999999</v>
+        <v>-4.194800000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>9.3391</v>
+        <v>-1.925</v>
       </c>
       <c r="L23" t="n">
-        <v>-15.0477</v>
+        <v>-2.27</v>
       </c>
       <c r="M23" t="n">
-        <v>-16.4202</v>
+        <v>-15.7769</v>
       </c>
       <c r="N23" t="n">
-        <v>-15.3244</v>
+        <v>-12.3435</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0956</v>
+        <v>-3.4331</v>
       </c>
       <c r="P23" t="n">
-        <v>14.1106</v>
+        <v>15.0269</v>
       </c>
       <c r="Q23" t="n">
-        <v>-26.3894</v>
+        <v>-12.4618</v>
       </c>
       <c r="R23" t="n">
-        <v>40.4997</v>
+        <v>27.4886</v>
       </c>
       <c r="S23" t="n">
-        <v>-24.2733</v>
+        <v>1.0031</v>
       </c>
       <c r="T23" t="n">
-        <v>-15.0642</v>
+        <v>1.1985</v>
       </c>
       <c r="U23" t="n">
-        <v>-9.2087</v>
+        <v>-0.195</v>
       </c>
       <c r="V23" t="n">
-        <v>8.0589</v>
+        <v>-10.2626</v>
       </c>
       <c r="W23" t="n">
-        <v>14.3212</v>
+        <v>3.1882</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.2622</v>
+        <v>-13.4509</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-65.49760000000001</v>
+        <v>-49.337</v>
       </c>
       <c r="E24" t="n">
-        <v>-60.8415</v>
+        <v>-50.8681</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.6558</v>
+        <v>1.5316</v>
       </c>
       <c r="G24" t="n">
         <v>-30.0512</v>
@@ -2326,13 +2326,13 @@
         <v>33.1693</v>
       </c>
       <c r="S24" t="n">
-        <v>-18.6181</v>
+        <v>-2.4574</v>
       </c>
       <c r="T24" t="n">
-        <v>-14.5447</v>
+        <v>-4.5711</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.0733</v>
+        <v>2.1139</v>
       </c>
       <c r="V24" t="n">
         <v>-14.9958</v>
@@ -2359,16 +2359,16 @@
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>223.0734999999999</v>
+        <v>247.5407</v>
       </c>
       <c r="E25" t="n">
-        <v>186.8142000000001</v>
+        <v>192.6904</v>
       </c>
       <c r="F25" t="n">
-        <v>36.2599</v>
+        <v>54.84950000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>84.95180000000002</v>
+        <v>84.95180000000005</v>
       </c>
       <c r="H25" t="n">
         <v>59.9338</v>
@@ -2383,7 +2383,7 @@
         <v>235.0796</v>
       </c>
       <c r="L25" t="n">
-        <v>64.18640000000002</v>
+        <v>64.18640000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-214.3161</v>
@@ -2395,22 +2395,22 @@
         <v>-39.1694</v>
       </c>
       <c r="P25" t="n">
-        <v>62.30689999999998</v>
+        <v>62.3069</v>
       </c>
       <c r="Q25" t="n">
         <v>-354.6046</v>
       </c>
       <c r="R25" t="n">
-        <v>416.9090000000001</v>
+        <v>416.909</v>
       </c>
       <c r="S25" t="n">
-        <v>13.5558</v>
+        <v>38.0213</v>
       </c>
       <c r="T25" t="n">
-        <v>5.408600000000005</v>
+        <v>11.2856</v>
       </c>
       <c r="U25" t="n">
-        <v>8.146999999999998</v>
+        <v>26.7373</v>
       </c>
       <c r="V25" t="n">
         <v>62.2595</v>
